--- a/artifacts/traceability_reports/all_requirements_traceability.xlsx
+++ b/artifacts/traceability_reports/all_requirements_traceability.xlsx
@@ -52617,7 +52617,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T14:21:00+00:00</t>
+          <t>2026-10-06T15:07:46+00:00</t>
         </is>
       </c>
     </row>
@@ -52653,7 +52653,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\data\canonical\canonical_store.sqlite</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\data\canonical\canonical_store.sqlite</t>
         </is>
       </c>
     </row>
@@ -52665,7 +52665,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\traceability_reports\all_requirements_traceability.xlsx</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\traceability_reports\all_requirements_traceability.xlsx</t>
         </is>
       </c>
     </row>
